--- a/Week1-Day2-ExcelFoundation-CoreFormula/KPMG_W1_Day1_Practice.xlsx
+++ b/Week1-Day2-ExcelFoundation-CoreFormula/KPMG_W1_Day1_Practice.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/ashujauhari/Data-2026/Client-2026/REVATURE-KPMG-OperationAnalyst/Week1-ExcelFoundation/Day2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84955792-C76D-4343-8C81-259F885F4F9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FDDEEC15-B47D-1442-AA91-BDD8B16A2F8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="18000" tabRatio="500" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Cleaned_Data-Practice" sheetId="6" r:id="rId1"/>
@@ -20,6 +20,7 @@
     <sheet name="Raw_Data" sheetId="2" r:id="rId5"/>
     <sheet name="Cleaned_Data" sheetId="3" r:id="rId6"/>
     <sheet name="Sorting_Lab" sheetId="8" r:id="rId7"/>
+    <sheet name="Reconciliation" sheetId="9" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -82,7 +83,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1249" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="463">
   <si>
     <t>KPMG Operations Analyst – Week 1 | Data Cleaning Practice</t>
   </si>
@@ -1325,19 +1326,167 @@
   </si>
   <si>
     <t>Count()</t>
+  </si>
+  <si>
+    <t>Reconciliation Demo — Ledger vs Bank Statement</t>
+  </si>
+  <si>
+    <t>Purpose: match every ledger transaction to the bank statement, explain every difference, and tie the two totals out to zero.</t>
+  </si>
+  <si>
+    <t>Matching tolerance (INR)</t>
+  </si>
+  <si>
+    <t>1. LEDGER (source: Cleaned_Data-Week1- Day 2)</t>
+  </si>
+  <si>
+    <t>2. BANK STATEMENT (imported — exercise data)</t>
+  </si>
+  <si>
+    <t>3. RECONCILIATION (ledger side)</t>
+  </si>
+  <si>
+    <t>Txn ID</t>
+  </si>
+  <si>
+    <t>Date</t>
+  </si>
+  <si>
+    <t>Type</t>
+  </si>
+  <si>
+    <t>Ledger Amount</t>
+  </si>
+  <si>
+    <t>Bank Amount</t>
+  </si>
+  <si>
+    <t>In Ledger?</t>
+  </si>
+  <si>
+    <t>Ledger count</t>
+  </si>
+  <si>
+    <t>Ledger Amt</t>
+  </si>
+  <si>
+    <t>Bank Amt</t>
+  </si>
+  <si>
+    <t>Difference</t>
+  </si>
+  <si>
+    <t>In Ledger</t>
+  </si>
+  <si>
+    <t>-</t>
+  </si>
+  <si>
+    <t>Matched</t>
+  </si>
+  <si>
+    <t>Duplicate ID - review</t>
+  </si>
+  <si>
+    <t>TXN-9001</t>
+  </si>
+  <si>
+    <t>Missing in Ledger</t>
+  </si>
+  <si>
+    <t>Amount Mismatch</t>
+  </si>
+  <si>
+    <t>Missing in Bank</t>
+  </si>
+  <si>
+    <t>4. SUMMARY &amp; TIE-OUT</t>
+  </si>
+  <si>
+    <t>OBJECTIVE OF THIS RECONCILIATION</t>
+  </si>
+  <si>
+    <t>Ledger total</t>
+  </si>
+  <si>
+    <t>Objective: prove that the transactions recorded in the company's ledger agree with the transactions recorded by the bank — and where they do not agree, identify and explain every difference.</t>
+  </si>
+  <si>
+    <t>Bank total</t>
+  </si>
+  <si>
+    <t>Why it matters: a reconciliation is the control that detects missing entries, duplicate postings, keying errors and unrecorded bank activity before they reach the financial statements.</t>
+  </si>
+  <si>
+    <t>Unexplained difference</t>
+  </si>
+  <si>
+    <t>Success test: the gross difference between the two totals must be fully accounted for by named reconciling items, leaving an unexplained difference of zero (cell B23).</t>
+  </si>
+  <si>
+    <t>Amount mismatches</t>
+  </si>
+  <si>
+    <t>METHOD (4 steps)</t>
+  </si>
+  <si>
+    <t>Step 1 — Prepare both populations: ledger (block 1, linked from the cleaned data) and bank statement (block 2, imported).</t>
+  </si>
+  <si>
+    <t>Duplicate IDs in ledger</t>
+  </si>
+  <si>
+    <t>Step 2 — Match on a unique key (Transaction ID) using INDEX/MATCH, and compare amounts within an agreed tolerance (cell B4).</t>
+  </si>
+  <si>
+    <t>Missing in Ledger (bank-only)</t>
+  </si>
+  <si>
+    <t>Step 3 — Classify every unmatched or differing row: Amount Mismatch, Missing in Bank, Missing in Ledger, or Duplicate ID.</t>
+  </si>
+  <si>
+    <t>Reconciling items (explained)</t>
+  </si>
+  <si>
+    <t>Step 4 — Bridge the two totals: list each exception as a reconciling item and confirm the residual is nil.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Amount mismatch differences</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Ledger-only items (missing in bank)</t>
+  </si>
+  <si>
+    <t>OUTCOME</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Duplicate ledger entries (excess)</t>
+  </si>
+  <si>
+    <t>Gross difference of 8,100.00 is explained by 5 exception(s); unexplained difference = 0.00.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">   Bank-only items (missing in ledger)</t>
+  </si>
+  <si>
+    <t>Reconciled?</t>
+  </si>
+  <si>
+    <t>YES - fully explained</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="dd\/mm\/yyyy"/>
     <numFmt numFmtId="165" formatCode="dd/mmm/yyyy"/>
     <numFmt numFmtId="166" formatCode="[$-1009]d/mmm/yy;@"/>
     <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00;[Red]&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="172" formatCode="#,##0.00;\(#,##0.00\);\-"/>
   </numFmts>
-  <fonts count="31" x14ac:knownFonts="1">
+  <fonts count="44" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1539,8 +1688,105 @@
       <name val="Courier New"/>
       <family val="1"/>
     </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <color rgb="FFC00000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF595959"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF008000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF404040"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="1"/>
+    </font>
   </fonts>
-  <fills count="20">
+  <fills count="29">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1653,6 +1899,60 @@
       <patternFill patternType="solid">
         <fgColor theme="8" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1F4E79"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF548235"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF7030A0"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE2EFDA"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE4DFEC"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -1855,7 +2155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="99">
+  <cellXfs count="126">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -2021,57 +2321,11 @@
     <xf numFmtId="0" fontId="11" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="19" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="1" fontId="11" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="1" fontId="11" fillId="18" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2086,6 +2340,89 @@
     <xf numFmtId="0" fontId="29" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="30" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="33" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="2" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="21" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="22" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="23" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="24" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="34" fillId="25" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="37" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="4" fontId="35" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="4" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="172" fontId="32" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="38" fillId="26" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="39" fillId="27" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="40" fillId="28" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="36" fillId="20" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="172" fontId="34" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="42" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="43" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -3403,9 +3740,9 @@
       <c r="K1" s="59" t="s">
         <v>412</v>
       </c>
-      <c r="M1" s="94"/>
-      <c r="N1" s="94"/>
-      <c r="O1" s="94"/>
+      <c r="M1" s="76"/>
+      <c r="N1" s="76"/>
+      <c r="O1" s="76"/>
     </row>
     <row r="2" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="61" t="str">
@@ -3453,9 +3790,9 @@
         <f>IF(COUNTIF($J$2:J2,J2)&gt;1,"DUPLICATE","OK")</f>
         <v>OK</v>
       </c>
-      <c r="M2" s="96"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
+      <c r="M2" s="78"/>
+      <c r="N2" s="77"/>
+      <c r="O2" s="77"/>
     </row>
     <row r="3" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="61" t="str">
@@ -3597,7 +3934,7 @@
         <f>IF(COUNTIF($J$2:J5,J5)&gt;1,"DUPLICATE","OK")</f>
         <v>OK</v>
       </c>
-      <c r="M5" s="98"/>
+      <c r="M5" s="80"/>
     </row>
     <row r="6" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="61" t="str">
@@ -3833,7 +4170,7 @@
         <f>IF(COUNTIF($J$2:J10,J10)&gt;1,"DUPLICATE","OK")</f>
         <v>OK</v>
       </c>
-      <c r="M10" s="97"/>
+      <c r="M10" s="79"/>
     </row>
     <row r="11" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="61" t="str">
@@ -3928,7 +4265,7 @@
         <f>IF(COUNTIF($J$2:J12,J12)&gt;1,"DUPLICATE","OK")</f>
         <v>OK</v>
       </c>
-      <c r="M12" s="97"/>
+      <c r="M12" s="79"/>
     </row>
     <row r="13" spans="1:15" ht="18" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="61" t="str">
@@ -4823,172 +5160,172 @@
       </c>
     </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A32" s="91"/>
-      <c r="B32" s="91"/>
-      <c r="C32" s="91"/>
-      <c r="D32" s="91"/>
-      <c r="E32" s="91" t="s">
+      <c r="A32" s="73"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="73"/>
+      <c r="D32" s="73"/>
+      <c r="E32" s="73" t="s">
         <v>413</v>
       </c>
-      <c r="F32" s="91">
+      <c r="F32" s="73">
         <f>COUNT(F2:F31)</f>
         <v>29</v>
       </c>
-      <c r="G32" s="91"/>
-      <c r="H32" s="91"/>
-      <c r="I32" s="91"/>
-      <c r="J32" s="91"/>
-      <c r="K32" s="91"/>
-      <c r="L32" s="92"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+      <c r="J32" s="73"/>
+      <c r="K32" s="73"/>
+      <c r="L32" s="74"/>
     </row>
     <row r="33" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A33" s="91"/>
-      <c r="B33" s="91"/>
-      <c r="C33" s="91"/>
-      <c r="D33" s="91"/>
-      <c r="E33" s="91"/>
-      <c r="F33" s="93">
+      <c r="A33" s="73"/>
+      <c r="B33" s="73"/>
+      <c r="C33" s="73"/>
+      <c r="D33" s="73"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="75">
         <f>SUM(F2:F31)</f>
         <v>282900.5</v>
       </c>
-      <c r="G33" s="91"/>
-      <c r="H33" s="91"/>
-      <c r="I33" s="91"/>
-      <c r="J33" s="91"/>
-      <c r="K33" s="91"/>
-      <c r="L33" s="92"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
+      <c r="J33" s="73"/>
+      <c r="K33" s="73"/>
+      <c r="L33" s="74"/>
     </row>
     <row r="34" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="76" t="s">
+      <c r="A34" s="85" t="s">
         <v>287</v>
       </c>
-      <c r="B34" s="76"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="85"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
     </row>
     <row r="36" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="77" t="s">
+      <c r="A36" s="86" t="s">
         <v>288</v>
       </c>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="77"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="86"/>
+      <c r="E36" s="86"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="86"/>
+      <c r="I36" s="86"/>
+      <c r="J36" s="86"/>
     </row>
     <row r="37" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B37" s="74" t="s">
+      <c r="B37" s="81" t="s">
         <v>290</v>
       </c>
-      <c r="C37" s="74"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="75" t="s">
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="82" t="s">
         <v>291</v>
       </c>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
     </row>
     <row r="38" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B38" s="74" t="s">
+      <c r="B38" s="81" t="s">
         <v>293</v>
       </c>
-      <c r="C38" s="74"/>
-      <c r="D38" s="74"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="75" t="s">
+      <c r="C38" s="81"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
     </row>
     <row r="39" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B39" s="74" t="s">
+      <c r="B39" s="81" t="s">
         <v>296</v>
       </c>
-      <c r="C39" s="74"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="75" t="s">
+      <c r="C39" s="81"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="82" t="s">
         <v>297</v>
       </c>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
     </row>
     <row r="40" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B40" s="74" t="s">
+      <c r="B40" s="81" t="s">
         <v>299</v>
       </c>
-      <c r="C40" s="74"/>
-      <c r="D40" s="74"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="75" t="s">
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="82" t="s">
         <v>300</v>
       </c>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75"/>
-      <c r="J40" s="75"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
     </row>
     <row r="41" spans="1:12" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B41" s="74" t="s">
+      <c r="B41" s="81" t="s">
         <v>302</v>
       </c>
-      <c r="C41" s="74"/>
-      <c r="D41" s="74"/>
-      <c r="E41" s="74"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="75" t="s">
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="82" t="s">
         <v>303</v>
       </c>
-      <c r="H41" s="75"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="75"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="82"/>
     </row>
     <row r="43" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="83" t="s">
         <v>304</v>
       </c>
-      <c r="B43" s="73"/>
-      <c r="C43" s="73"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="73"/>
-      <c r="F43" s="73"/>
-      <c r="G43" s="73"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="73"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="83"/>
+      <c r="J43" s="83"/>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="C47" s="71">
@@ -4999,12 +5336,6 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="G37:J37"/>
-    <mergeCell ref="B38:F38"/>
-    <mergeCell ref="G38:J38"/>
     <mergeCell ref="A43:J43"/>
     <mergeCell ref="B39:F39"/>
     <mergeCell ref="G39:J39"/>
@@ -5012,6 +5343,12 @@
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="G41:J41"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="G37:J37"/>
+    <mergeCell ref="B38:F38"/>
+    <mergeCell ref="G38:J38"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -6124,19 +6461,19 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="78" t="s">
+      <c r="A33" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="B33" s="78"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="87"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="87"/>
+      <c r="K33" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -7238,19 +7575,19 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="78" t="s">
+      <c r="A33" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="B33" s="78"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="87"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="87"/>
+      <c r="K33" s="87"/>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="D37" s="18"/>
@@ -7293,41 +7630,41 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:4" ht="36" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B1" s="79" t="s">
+      <c r="B1" s="90" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
+      <c r="C1" s="90"/>
+      <c r="D1" s="90"/>
     </row>
     <row r="2" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B2" s="80" t="s">
+      <c r="B2" s="91" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="80"/>
-      <c r="D2" s="80"/>
+      <c r="C2" s="91"/>
+      <c r="D2" s="91"/>
     </row>
     <row r="3" spans="2:4" ht="9.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="4" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B4" s="81" t="s">
+      <c r="B4" s="88" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="81"/>
-      <c r="D4" s="81"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
     </row>
     <row r="5" spans="2:4" ht="43.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B5" s="82" t="s">
+      <c r="B5" s="92" t="s">
         <v>3</v>
       </c>
-      <c r="C5" s="82"/>
-      <c r="D5" s="82"/>
+      <c r="C5" s="92"/>
+      <c r="D5" s="92"/>
     </row>
     <row r="6" spans="2:4" ht="7.5" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="7" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B7" s="81" t="s">
+      <c r="B7" s="88" t="s">
         <v>4</v>
       </c>
-      <c r="C7" s="81"/>
-      <c r="D7" s="81"/>
+      <c r="C7" s="88"/>
+      <c r="D7" s="88"/>
     </row>
     <row r="8" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B8" s="1" t="s">
@@ -7435,60 +7772,60 @@
       </c>
     </row>
     <row r="18" spans="2:4" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B18" s="81" t="s">
+      <c r="B18" s="88" t="s">
         <v>26</v>
       </c>
-      <c r="C18" s="81"/>
-      <c r="D18" s="81"/>
+      <c r="C18" s="88"/>
+      <c r="D18" s="88"/>
     </row>
     <row r="19" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B19" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="D19" s="83"/>
+      <c r="D19" s="89"/>
     </row>
     <row r="20" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B20" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="C20" s="83" t="s">
+      <c r="C20" s="89" t="s">
         <v>30</v>
       </c>
-      <c r="D20" s="83"/>
+      <c r="D20" s="89"/>
     </row>
     <row r="21" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B21" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C21" s="83" t="s">
+      <c r="C21" s="89" t="s">
         <v>32</v>
       </c>
-      <c r="D21" s="83"/>
+      <c r="D21" s="89"/>
     </row>
     <row r="22" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="B22" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="C22" s="83" t="s">
+      <c r="C22" s="89" t="s">
         <v>34</v>
       </c>
-      <c r="D22" s="83"/>
+      <c r="D22" s="89"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B1:D1"/>
+    <mergeCell ref="B2:D2"/>
+    <mergeCell ref="B4:D4"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="B7:D7"/>
     <mergeCell ref="B18:D18"/>
     <mergeCell ref="C19:D19"/>
     <mergeCell ref="C20:D20"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C22:D22"/>
-    <mergeCell ref="B1:D1"/>
-    <mergeCell ref="B2:D2"/>
-    <mergeCell ref="B4:D4"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="B7:D7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -8598,19 +8935,19 @@
       </c>
     </row>
     <row r="33" spans="1:11" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A33" s="78" t="s">
+      <c r="A33" s="87" t="s">
         <v>279</v>
       </c>
-      <c r="B33" s="78"/>
-      <c r="C33" s="78"/>
-      <c r="D33" s="78"/>
-      <c r="E33" s="78"/>
-      <c r="F33" s="78"/>
-      <c r="G33" s="78"/>
-      <c r="H33" s="78"/>
-      <c r="I33" s="78"/>
-      <c r="J33" s="78"/>
-      <c r="K33" s="78"/>
+      <c r="B33" s="87"/>
+      <c r="C33" s="87"/>
+      <c r="D33" s="87"/>
+      <c r="E33" s="87"/>
+      <c r="F33" s="87"/>
+      <c r="G33" s="87"/>
+      <c r="H33" s="87"/>
+      <c r="I33" s="87"/>
+      <c r="J33" s="87"/>
+      <c r="K33" s="87"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -10068,139 +10405,144 @@
       </c>
     </row>
     <row r="34" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="76" t="s">
+      <c r="A34" s="85" t="s">
         <v>287</v>
       </c>
-      <c r="B34" s="76"/>
-      <c r="C34" s="76"/>
-      <c r="D34" s="76"/>
-      <c r="E34" s="76"/>
-      <c r="F34" s="76"/>
-      <c r="G34" s="76"/>
-      <c r="H34" s="76"/>
-      <c r="I34" s="76"/>
-      <c r="J34" s="76"/>
+      <c r="B34" s="85"/>
+      <c r="C34" s="85"/>
+      <c r="D34" s="85"/>
+      <c r="E34" s="85"/>
+      <c r="F34" s="85"/>
+      <c r="G34" s="85"/>
+      <c r="H34" s="85"/>
+      <c r="I34" s="85"/>
+      <c r="J34" s="85"/>
     </row>
     <row r="36" spans="1:10" ht="24" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A36" s="77" t="s">
+      <c r="A36" s="86" t="s">
         <v>288</v>
       </c>
-      <c r="B36" s="77"/>
-      <c r="C36" s="77"/>
-      <c r="D36" s="77"/>
-      <c r="E36" s="77"/>
-      <c r="F36" s="77"/>
-      <c r="G36" s="77"/>
-      <c r="H36" s="77"/>
-      <c r="I36" s="77"/>
-      <c r="J36" s="77"/>
+      <c r="B36" s="86"/>
+      <c r="C36" s="86"/>
+      <c r="D36" s="86"/>
+      <c r="E36" s="86"/>
+      <c r="F36" s="86"/>
+      <c r="G36" s="86"/>
+      <c r="H36" s="86"/>
+      <c r="I36" s="86"/>
+      <c r="J36" s="86"/>
     </row>
     <row r="37" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A37" s="1" t="s">
         <v>289</v>
       </c>
-      <c r="B37" s="74" t="s">
+      <c r="B37" s="81" t="s">
         <v>290</v>
       </c>
-      <c r="C37" s="74"/>
-      <c r="D37" s="74"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="75" t="s">
+      <c r="C37" s="81"/>
+      <c r="D37" s="81"/>
+      <c r="E37" s="81"/>
+      <c r="F37" s="81"/>
+      <c r="G37" s="82" t="s">
         <v>291</v>
       </c>
-      <c r="H37" s="75"/>
-      <c r="I37" s="75"/>
-      <c r="J37" s="75"/>
+      <c r="H37" s="82"/>
+      <c r="I37" s="82"/>
+      <c r="J37" s="82"/>
     </row>
     <row r="38" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A38" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="B38" s="74" t="s">
+      <c r="B38" s="81" t="s">
         <v>293</v>
       </c>
-      <c r="C38" s="74"/>
-      <c r="D38" s="74"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="75" t="s">
+      <c r="C38" s="81"/>
+      <c r="D38" s="81"/>
+      <c r="E38" s="81"/>
+      <c r="F38" s="81"/>
+      <c r="G38" s="82" t="s">
         <v>294</v>
       </c>
-      <c r="H38" s="75"/>
-      <c r="I38" s="75"/>
-      <c r="J38" s="75"/>
+      <c r="H38" s="82"/>
+      <c r="I38" s="82"/>
+      <c r="J38" s="82"/>
     </row>
     <row r="39" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A39" s="1" t="s">
         <v>295</v>
       </c>
-      <c r="B39" s="74" t="s">
+      <c r="B39" s="81" t="s">
         <v>296</v>
       </c>
-      <c r="C39" s="74"/>
-      <c r="D39" s="74"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="75" t="s">
+      <c r="C39" s="81"/>
+      <c r="D39" s="81"/>
+      <c r="E39" s="81"/>
+      <c r="F39" s="81"/>
+      <c r="G39" s="82" t="s">
         <v>297</v>
       </c>
-      <c r="H39" s="75"/>
-      <c r="I39" s="75"/>
-      <c r="J39" s="75"/>
+      <c r="H39" s="82"/>
+      <c r="I39" s="82"/>
+      <c r="J39" s="82"/>
     </row>
     <row r="40" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A40" s="1" t="s">
         <v>298</v>
       </c>
-      <c r="B40" s="74" t="s">
+      <c r="B40" s="81" t="s">
         <v>299</v>
       </c>
-      <c r="C40" s="74"/>
-      <c r="D40" s="74"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="75" t="s">
+      <c r="C40" s="81"/>
+      <c r="D40" s="81"/>
+      <c r="E40" s="81"/>
+      <c r="F40" s="81"/>
+      <c r="G40" s="82" t="s">
         <v>300</v>
       </c>
-      <c r="H40" s="75"/>
-      <c r="I40" s="75"/>
-      <c r="J40" s="75"/>
+      <c r="H40" s="82"/>
+      <c r="I40" s="82"/>
+      <c r="J40" s="82"/>
     </row>
     <row r="41" spans="1:10" ht="21.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A41" s="1" t="s">
         <v>301</v>
       </c>
-      <c r="B41" s="74" t="s">
+      <c r="B41" s="81" t="s">
         <v>302</v>
       </c>
-      <c r="C41" s="74"/>
-      <c r="D41" s="74"/>
-      <c r="E41" s="74"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="75" t="s">
+      <c r="C41" s="81"/>
+      <c r="D41" s="81"/>
+      <c r="E41" s="81"/>
+      <c r="F41" s="81"/>
+      <c r="G41" s="82" t="s">
         <v>303</v>
       </c>
-      <c r="H41" s="75"/>
-      <c r="I41" s="75"/>
-      <c r="J41" s="75"/>
+      <c r="H41" s="82"/>
+      <c r="I41" s="82"/>
+      <c r="J41" s="82"/>
     </row>
     <row r="43" spans="1:10" ht="18" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A43" s="73" t="s">
+      <c r="A43" s="83" t="s">
         <v>304</v>
       </c>
-      <c r="B43" s="73"/>
-      <c r="C43" s="73"/>
-      <c r="D43" s="73"/>
-      <c r="E43" s="73"/>
-      <c r="F43" s="73"/>
-      <c r="G43" s="73"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="73"/>
-      <c r="J43" s="73"/>
+      <c r="B43" s="83"/>
+      <c r="C43" s="83"/>
+      <c r="D43" s="83"/>
+      <c r="E43" s="83"/>
+      <c r="F43" s="83"/>
+      <c r="G43" s="83"/>
+      <c r="H43" s="83"/>
+      <c r="I43" s="83"/>
+      <c r="J43" s="83"/>
     </row>
   </sheetData>
   <mergeCells count="14">
+    <mergeCell ref="A2:J2"/>
+    <mergeCell ref="A34:J34"/>
+    <mergeCell ref="A36:J36"/>
+    <mergeCell ref="B37:F37"/>
+    <mergeCell ref="G37:J37"/>
     <mergeCell ref="B41:F41"/>
     <mergeCell ref="G41:J41"/>
     <mergeCell ref="A43:J43"/>
@@ -10210,11 +10552,6 @@
     <mergeCell ref="G39:J39"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="G40:J40"/>
-    <mergeCell ref="A2:J2"/>
-    <mergeCell ref="A34:J34"/>
-    <mergeCell ref="A36:J36"/>
-    <mergeCell ref="B37:F37"/>
-    <mergeCell ref="G37:J37"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -10234,34 +10571,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="2:7" ht="19" x14ac:dyDescent="0.2">
-      <c r="B1" s="87" t="s">
+      <c r="B1" s="95" t="s">
         <v>306</v>
       </c>
-      <c r="C1" s="87"/>
-      <c r="D1" s="87"/>
-      <c r="E1" s="87"/>
-      <c r="F1" s="87"/>
-      <c r="G1" s="87"/>
+      <c r="C1" s="95"/>
+      <c r="D1" s="95"/>
+      <c r="E1" s="95"/>
+      <c r="F1" s="95"/>
+      <c r="G1" s="95"/>
     </row>
     <row r="2" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B2" s="88" t="s">
+      <c r="B2" s="96" t="s">
         <v>307</v>
       </c>
-      <c r="C2" s="88"/>
-      <c r="D2" s="88"/>
-      <c r="E2" s="88"/>
-      <c r="F2" s="88"/>
-      <c r="G2" s="88"/>
+      <c r="C2" s="96"/>
+      <c r="D2" s="96"/>
+      <c r="E2" s="96"/>
+      <c r="F2" s="96"/>
+      <c r="G2" s="96"/>
     </row>
     <row r="4" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B4" s="85" t="s">
+      <c r="B4" s="93" t="s">
         <v>308</v>
       </c>
-      <c r="C4" s="85"/>
-      <c r="D4" s="85"/>
-      <c r="E4" s="85"/>
-      <c r="F4" s="85"/>
-      <c r="G4" s="85"/>
+      <c r="C4" s="93"/>
+      <c r="D4" s="93"/>
+      <c r="E4" s="93"/>
+      <c r="F4" s="93"/>
+      <c r="G4" s="93"/>
     </row>
     <row r="5" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B5" s="31" t="s">
@@ -10299,34 +10636,34 @@
       </c>
     </row>
     <row r="13" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="85" t="s">
+      <c r="B13" s="93" t="s">
         <v>316</v>
       </c>
-      <c r="C13" s="85"/>
-      <c r="D13" s="85"/>
-      <c r="E13" s="85"/>
-      <c r="F13" s="85"/>
-      <c r="G13" s="85"/>
+      <c r="C13" s="93"/>
+      <c r="D13" s="93"/>
+      <c r="E13" s="93"/>
+      <c r="F13" s="93"/>
+      <c r="G13" s="93"/>
     </row>
     <row r="14" spans="2:7" ht="42" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="B14" s="89" t="s">
+      <c r="B14" s="97" t="s">
         <v>317</v>
       </c>
-      <c r="C14" s="90"/>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="90"/>
-      <c r="G14" s="90"/>
+      <c r="C14" s="98"/>
+      <c r="D14" s="98"/>
+      <c r="E14" s="98"/>
+      <c r="F14" s="98"/>
+      <c r="G14" s="98"/>
     </row>
     <row r="16" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B16" s="85" t="s">
+      <c r="B16" s="93" t="s">
         <v>318</v>
       </c>
-      <c r="C16" s="85"/>
-      <c r="D16" s="85"/>
-      <c r="E16" s="85"/>
-      <c r="F16" s="85"/>
-      <c r="G16" s="85"/>
+      <c r="C16" s="93"/>
+      <c r="D16" s="93"/>
+      <c r="E16" s="93"/>
+      <c r="F16" s="93"/>
+      <c r="G16" s="93"/>
     </row>
     <row r="17" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B17" s="32" t="s">
@@ -10889,12 +11226,12 @@
       </c>
     </row>
     <row r="46" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B46" s="85" t="s">
+      <c r="B46" s="93" t="s">
         <v>341</v>
       </c>
-      <c r="C46" s="85"/>
-      <c r="D46" s="85"/>
-      <c r="E46" s="85"/>
+      <c r="C46" s="93"/>
+      <c r="D46" s="93"/>
+      <c r="E46" s="93"/>
     </row>
     <row r="47" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B47" s="50" t="s">
@@ -11037,11 +11374,11 @@
       </c>
     </row>
     <row r="58" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B58" s="85" t="s">
+      <c r="B58" s="93" t="s">
         <v>382</v>
       </c>
-      <c r="C58" s="85"/>
-      <c r="D58" s="85"/>
+      <c r="C58" s="93"/>
+      <c r="D58" s="93"/>
     </row>
     <row r="59" spans="2:5" x14ac:dyDescent="0.2">
       <c r="B59" s="47" t="s">
@@ -11127,12 +11464,12 @@
       </c>
     </row>
     <row r="67" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B67" s="86" t="s">
+      <c r="B67" s="94" t="s">
         <v>398</v>
       </c>
-      <c r="C67" s="86"/>
-      <c r="D67" s="86"/>
-      <c r="E67" s="86"/>
+      <c r="C67" s="94"/>
+      <c r="D67" s="94"/>
+      <c r="E67" s="94"/>
     </row>
     <row r="68" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B68" s="43" t="s">
@@ -11671,4 +12008,956 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D3BF94C-E875-7E45-94E0-AAD7CE485ACE}">
+  <dimension ref="A1:N34"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="10" max="10" width="25.5" customWidth="1"/>
+    <col min="14" max="14" width="27" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14" ht="19" x14ac:dyDescent="0.25">
+      <c r="A1" s="99" t="s">
+        <v>414</v>
+      </c>
+      <c r="B1" s="99"/>
+      <c r="C1" s="99"/>
+      <c r="D1" s="100"/>
+      <c r="E1" s="100"/>
+      <c r="F1" s="100"/>
+      <c r="G1" s="100"/>
+      <c r="H1" s="100"/>
+      <c r="I1" s="100"/>
+      <c r="J1" s="100"/>
+      <c r="K1" s="100"/>
+      <c r="L1" s="100"/>
+      <c r="M1" s="100"/>
+      <c r="N1" s="100"/>
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A2" s="101" t="s">
+        <v>415</v>
+      </c>
+      <c r="B2" s="101"/>
+      <c r="C2" s="101"/>
+      <c r="D2" s="101"/>
+      <c r="E2" s="101"/>
+      <c r="F2" s="101"/>
+      <c r="G2" s="101"/>
+      <c r="H2" s="100"/>
+      <c r="I2" s="100"/>
+      <c r="J2" s="100"/>
+      <c r="K2" s="100"/>
+      <c r="L2" s="100"/>
+      <c r="M2" s="100"/>
+      <c r="N2" s="100"/>
+    </row>
+    <row r="3" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A3" s="100"/>
+      <c r="B3" s="100"/>
+      <c r="C3" s="100"/>
+      <c r="D3" s="100"/>
+      <c r="E3" s="100"/>
+      <c r="F3" s="100"/>
+      <c r="G3" s="100"/>
+      <c r="H3" s="100"/>
+      <c r="I3" s="100"/>
+      <c r="J3" s="100"/>
+      <c r="K3" s="100"/>
+      <c r="L3" s="100"/>
+      <c r="M3" s="100"/>
+      <c r="N3" s="100"/>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A4" s="102" t="s">
+        <v>416</v>
+      </c>
+      <c r="B4" s="103">
+        <v>1</v>
+      </c>
+      <c r="C4" s="100"/>
+      <c r="D4" s="100"/>
+      <c r="E4" s="100"/>
+      <c r="F4" s="100"/>
+      <c r="G4" s="100"/>
+      <c r="H4" s="100"/>
+      <c r="I4" s="100"/>
+      <c r="J4" s="100"/>
+      <c r="K4" s="100"/>
+      <c r="L4" s="100"/>
+      <c r="M4" s="100"/>
+      <c r="N4" s="100"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A5" s="100"/>
+      <c r="B5" s="100"/>
+      <c r="C5" s="100"/>
+      <c r="D5" s="100"/>
+      <c r="E5" s="100"/>
+      <c r="F5" s="100"/>
+      <c r="G5" s="100"/>
+      <c r="H5" s="100"/>
+      <c r="I5" s="100"/>
+      <c r="J5" s="100"/>
+      <c r="K5" s="100"/>
+      <c r="L5" s="100"/>
+      <c r="M5" s="100"/>
+      <c r="N5" s="100"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A6" s="104" t="s">
+        <v>417</v>
+      </c>
+      <c r="B6" s="100"/>
+      <c r="C6" s="100"/>
+      <c r="D6" s="100"/>
+      <c r="E6" s="100"/>
+      <c r="F6" s="105" t="s">
+        <v>418</v>
+      </c>
+      <c r="G6" s="100"/>
+      <c r="H6" s="100"/>
+      <c r="I6" s="100"/>
+      <c r="J6" s="106" t="s">
+        <v>419</v>
+      </c>
+      <c r="K6" s="100"/>
+      <c r="L6" s="100"/>
+      <c r="M6" s="100"/>
+      <c r="N6" s="100"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A7" s="107" t="s">
+        <v>420</v>
+      </c>
+      <c r="B7" s="107" t="s">
+        <v>421</v>
+      </c>
+      <c r="C7" s="107" t="s">
+        <v>422</v>
+      </c>
+      <c r="D7" s="107" t="s">
+        <v>423</v>
+      </c>
+      <c r="E7" s="100"/>
+      <c r="F7" s="108" t="s">
+        <v>420</v>
+      </c>
+      <c r="G7" s="108" t="s">
+        <v>424</v>
+      </c>
+      <c r="H7" s="108" t="s">
+        <v>425</v>
+      </c>
+      <c r="I7" s="108" t="s">
+        <v>426</v>
+      </c>
+      <c r="J7" s="109" t="s">
+        <v>420</v>
+      </c>
+      <c r="K7" s="109" t="s">
+        <v>427</v>
+      </c>
+      <c r="L7" s="109" t="s">
+        <v>428</v>
+      </c>
+      <c r="M7" s="109" t="s">
+        <v>429</v>
+      </c>
+      <c r="N7" s="109" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A8" s="110" t="s">
+        <v>54</v>
+      </c>
+      <c r="B8" s="111">
+        <v>46235</v>
+      </c>
+      <c r="C8" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D8" s="112">
+        <v>15000</v>
+      </c>
+      <c r="E8" s="100"/>
+      <c r="F8" s="113" t="s">
+        <v>54</v>
+      </c>
+      <c r="G8" s="114">
+        <v>15000</v>
+      </c>
+      <c r="H8" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="I8" s="100">
+        <v>1</v>
+      </c>
+      <c r="J8" s="100" t="s">
+        <v>54</v>
+      </c>
+      <c r="K8" s="115">
+        <v>15000</v>
+      </c>
+      <c r="L8" s="115">
+        <v>15000</v>
+      </c>
+      <c r="M8" s="116" t="s">
+        <v>431</v>
+      </c>
+      <c r="N8" s="117" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A9" s="110" t="s">
+        <v>64</v>
+      </c>
+      <c r="B9" s="111">
+        <v>46236</v>
+      </c>
+      <c r="C9" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="D9" s="112">
+        <v>8500</v>
+      </c>
+      <c r="E9" s="100"/>
+      <c r="F9" s="113" t="s">
+        <v>64</v>
+      </c>
+      <c r="G9" s="114">
+        <v>8500</v>
+      </c>
+      <c r="H9" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="I9" s="100">
+        <v>1</v>
+      </c>
+      <c r="J9" s="100" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="115">
+        <v>8500</v>
+      </c>
+      <c r="L9" s="115">
+        <v>8500</v>
+      </c>
+      <c r="M9" s="116" t="s">
+        <v>431</v>
+      </c>
+      <c r="N9" s="117" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A10" s="110" t="s">
+        <v>73</v>
+      </c>
+      <c r="B10" s="110" t="s">
+        <v>70</v>
+      </c>
+      <c r="C10" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D10" s="112">
+        <v>22000</v>
+      </c>
+      <c r="E10" s="100"/>
+      <c r="F10" s="113" t="s">
+        <v>73</v>
+      </c>
+      <c r="G10" s="114">
+        <v>22000</v>
+      </c>
+      <c r="H10" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="I10" s="100">
+        <v>2</v>
+      </c>
+      <c r="J10" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="K10" s="115">
+        <v>22000</v>
+      </c>
+      <c r="L10" s="115">
+        <v>22000</v>
+      </c>
+      <c r="M10" s="116" t="s">
+        <v>431</v>
+      </c>
+      <c r="N10" s="118" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A11" s="110" t="s">
+        <v>82</v>
+      </c>
+      <c r="B11" s="111">
+        <v>46238</v>
+      </c>
+      <c r="C11" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="112">
+        <v>3750</v>
+      </c>
+      <c r="E11" s="100"/>
+      <c r="F11" s="113" t="s">
+        <v>82</v>
+      </c>
+      <c r="G11" s="114">
+        <v>3750</v>
+      </c>
+      <c r="H11" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="I11" s="100">
+        <v>1</v>
+      </c>
+      <c r="J11" s="100" t="s">
+        <v>82</v>
+      </c>
+      <c r="K11" s="115">
+        <v>3750</v>
+      </c>
+      <c r="L11" s="115">
+        <v>3750</v>
+      </c>
+      <c r="M11" s="116" t="s">
+        <v>431</v>
+      </c>
+      <c r="N11" s="117" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A12" s="110" t="s">
+        <v>73</v>
+      </c>
+      <c r="B12" s="111">
+        <v>46239</v>
+      </c>
+      <c r="C12" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="112">
+        <v>9800</v>
+      </c>
+      <c r="E12" s="100"/>
+      <c r="F12" s="113" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="114">
+        <v>1200.5</v>
+      </c>
+      <c r="H12" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="I12" s="100">
+        <v>1</v>
+      </c>
+      <c r="J12" s="100" t="s">
+        <v>73</v>
+      </c>
+      <c r="K12" s="115">
+        <v>9800</v>
+      </c>
+      <c r="L12" s="115">
+        <v>22000</v>
+      </c>
+      <c r="M12" s="116">
+        <v>-12200</v>
+      </c>
+      <c r="N12" s="118" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A13" s="110" t="s">
+        <v>98</v>
+      </c>
+      <c r="B13" s="111">
+        <v>46240</v>
+      </c>
+      <c r="C13" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="D13" s="112">
+        <v>1200.5</v>
+      </c>
+      <c r="E13" s="100"/>
+      <c r="F13" s="113" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="114">
+        <v>500</v>
+      </c>
+      <c r="H13" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="I13" s="100">
+        <v>1</v>
+      </c>
+      <c r="J13" s="100" t="s">
+        <v>98</v>
+      </c>
+      <c r="K13" s="115">
+        <v>1200.5</v>
+      </c>
+      <c r="L13" s="115">
+        <v>1200.5</v>
+      </c>
+      <c r="M13" s="116" t="s">
+        <v>431</v>
+      </c>
+      <c r="N13" s="117" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A14" s="110" t="s">
+        <v>108</v>
+      </c>
+      <c r="B14" s="111">
+        <v>46241</v>
+      </c>
+      <c r="C14" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="D14" s="112">
+        <v>500</v>
+      </c>
+      <c r="E14" s="100"/>
+      <c r="F14" s="113" t="s">
+        <v>116</v>
+      </c>
+      <c r="G14" s="114">
+        <v>45000</v>
+      </c>
+      <c r="H14" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="I14" s="100">
+        <v>1</v>
+      </c>
+      <c r="J14" s="100" t="s">
+        <v>108</v>
+      </c>
+      <c r="K14" s="115">
+        <v>500</v>
+      </c>
+      <c r="L14" s="115">
+        <v>500</v>
+      </c>
+      <c r="M14" s="116" t="s">
+        <v>431</v>
+      </c>
+      <c r="N14" s="117" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A15" s="110" t="s">
+        <v>116</v>
+      </c>
+      <c r="B15" s="111">
+        <v>46242</v>
+      </c>
+      <c r="C15" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D15" s="112">
+        <v>45000</v>
+      </c>
+      <c r="E15" s="100"/>
+      <c r="F15" s="113" t="s">
+        <v>124</v>
+      </c>
+      <c r="G15" s="114">
+        <v>2300</v>
+      </c>
+      <c r="H15" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="I15" s="100">
+        <v>1</v>
+      </c>
+      <c r="J15" s="100" t="s">
+        <v>116</v>
+      </c>
+      <c r="K15" s="115">
+        <v>45000</v>
+      </c>
+      <c r="L15" s="115">
+        <v>45000</v>
+      </c>
+      <c r="M15" s="116" t="s">
+        <v>431</v>
+      </c>
+      <c r="N15" s="117" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A16" s="110" t="s">
+        <v>124</v>
+      </c>
+      <c r="B16" s="111">
+        <v>46243</v>
+      </c>
+      <c r="C16" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="D16" s="112">
+        <v>2300</v>
+      </c>
+      <c r="E16" s="100"/>
+      <c r="F16" s="113" t="s">
+        <v>132</v>
+      </c>
+      <c r="G16" s="114">
+        <v>11500</v>
+      </c>
+      <c r="H16" s="100" t="s">
+        <v>430</v>
+      </c>
+      <c r="I16" s="100">
+        <v>1</v>
+      </c>
+      <c r="J16" s="100" t="s">
+        <v>124</v>
+      </c>
+      <c r="K16" s="115">
+        <v>2300</v>
+      </c>
+      <c r="L16" s="115">
+        <v>2300</v>
+      </c>
+      <c r="M16" s="116" t="s">
+        <v>431</v>
+      </c>
+      <c r="N16" s="117" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A17" s="110" t="s">
+        <v>132</v>
+      </c>
+      <c r="B17" s="111">
+        <v>46244</v>
+      </c>
+      <c r="C17" s="110" t="s">
+        <v>50</v>
+      </c>
+      <c r="D17" s="112">
+        <v>11000</v>
+      </c>
+      <c r="E17" s="100"/>
+      <c r="F17" s="113" t="s">
+        <v>434</v>
+      </c>
+      <c r="G17" s="114">
+        <v>1950</v>
+      </c>
+      <c r="H17" s="118" t="s">
+        <v>435</v>
+      </c>
+      <c r="I17" s="100">
+        <v>0</v>
+      </c>
+      <c r="J17" s="100" t="s">
+        <v>132</v>
+      </c>
+      <c r="K17" s="115">
+        <v>11000</v>
+      </c>
+      <c r="L17" s="115">
+        <v>11500</v>
+      </c>
+      <c r="M17" s="116">
+        <v>-500</v>
+      </c>
+      <c r="N17" s="119" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A18" s="110" t="s">
+        <v>141</v>
+      </c>
+      <c r="B18" s="111">
+        <v>46245</v>
+      </c>
+      <c r="C18" s="110" t="s">
+        <v>80</v>
+      </c>
+      <c r="D18" s="112">
+        <v>750</v>
+      </c>
+      <c r="E18" s="100"/>
+      <c r="F18" s="100"/>
+      <c r="G18" s="100"/>
+      <c r="H18" s="100"/>
+      <c r="I18" s="100"/>
+      <c r="J18" s="100" t="s">
+        <v>141</v>
+      </c>
+      <c r="K18" s="115">
+        <v>750</v>
+      </c>
+      <c r="L18" s="115"/>
+      <c r="M18" s="116"/>
+      <c r="N18" s="118" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A19" s="100"/>
+      <c r="B19" s="100"/>
+      <c r="C19" s="100"/>
+      <c r="D19" s="100"/>
+      <c r="E19" s="100"/>
+      <c r="F19" s="100"/>
+      <c r="G19" s="100"/>
+      <c r="H19" s="100"/>
+      <c r="I19" s="100"/>
+      <c r="J19" s="100"/>
+      <c r="K19" s="100"/>
+      <c r="L19" s="100"/>
+      <c r="M19" s="100"/>
+      <c r="N19" s="100"/>
+    </row>
+    <row r="20" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A20" s="104" t="s">
+        <v>438</v>
+      </c>
+      <c r="B20" s="100"/>
+      <c r="C20" s="100"/>
+      <c r="D20" s="120" t="s">
+        <v>439</v>
+      </c>
+      <c r="E20" s="100"/>
+      <c r="F20" s="100"/>
+      <c r="G20" s="100"/>
+      <c r="H20" s="100"/>
+      <c r="I20" s="100"/>
+      <c r="J20" s="100"/>
+      <c r="K20" s="100"/>
+      <c r="L20" s="100"/>
+      <c r="M20" s="100"/>
+      <c r="N20" s="100"/>
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A21" s="100" t="s">
+        <v>440</v>
+      </c>
+      <c r="B21" s="115">
+        <v>119800.5</v>
+      </c>
+      <c r="C21" s="100"/>
+      <c r="D21" s="121" t="s">
+        <v>441</v>
+      </c>
+      <c r="E21" s="121"/>
+      <c r="F21" s="121"/>
+      <c r="G21" s="121"/>
+      <c r="H21" s="121"/>
+      <c r="I21" s="121"/>
+      <c r="J21" s="121"/>
+      <c r="K21" s="121"/>
+      <c r="L21" s="121"/>
+      <c r="M21" s="121"/>
+      <c r="N21" s="121"/>
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A22" s="100" t="s">
+        <v>442</v>
+      </c>
+      <c r="B22" s="115">
+        <v>111700.5</v>
+      </c>
+      <c r="C22" s="100"/>
+      <c r="D22" s="121" t="s">
+        <v>443</v>
+      </c>
+      <c r="E22" s="121"/>
+      <c r="F22" s="121"/>
+      <c r="G22" s="121"/>
+      <c r="H22" s="121"/>
+      <c r="I22" s="121"/>
+      <c r="J22" s="121"/>
+      <c r="K22" s="121"/>
+      <c r="L22" s="121"/>
+      <c r="M22" s="121"/>
+      <c r="N22" s="121"/>
+    </row>
+    <row r="23" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A23" s="102" t="s">
+        <v>444</v>
+      </c>
+      <c r="B23" s="122" t="s">
+        <v>431</v>
+      </c>
+      <c r="C23" s="100"/>
+      <c r="D23" s="121" t="s">
+        <v>445</v>
+      </c>
+      <c r="E23" s="121"/>
+      <c r="F23" s="121"/>
+      <c r="G23" s="121"/>
+      <c r="H23" s="121"/>
+      <c r="I23" s="121"/>
+      <c r="J23" s="121"/>
+      <c r="K23" s="121"/>
+      <c r="L23" s="121"/>
+      <c r="M23" s="121"/>
+      <c r="N23" s="100"/>
+    </row>
+    <row r="24" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A24" s="100" t="s">
+        <v>432</v>
+      </c>
+      <c r="B24" s="100">
+        <v>7</v>
+      </c>
+      <c r="C24" s="100"/>
+      <c r="D24" s="123"/>
+      <c r="E24" s="100"/>
+      <c r="F24" s="100"/>
+      <c r="G24" s="100"/>
+      <c r="H24" s="100"/>
+      <c r="I24" s="100"/>
+      <c r="J24" s="100"/>
+      <c r="K24" s="100"/>
+      <c r="L24" s="100"/>
+      <c r="M24" s="100"/>
+      <c r="N24" s="100"/>
+    </row>
+    <row r="25" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A25" s="100" t="s">
+        <v>446</v>
+      </c>
+      <c r="B25" s="100">
+        <v>1</v>
+      </c>
+      <c r="C25" s="100"/>
+      <c r="D25" s="120" t="s">
+        <v>447</v>
+      </c>
+      <c r="E25" s="100"/>
+      <c r="F25" s="100"/>
+      <c r="G25" s="100"/>
+      <c r="H25" s="100"/>
+      <c r="I25" s="100"/>
+      <c r="J25" s="100"/>
+      <c r="K25" s="100"/>
+      <c r="L25" s="100"/>
+      <c r="M25" s="100"/>
+      <c r="N25" s="100"/>
+    </row>
+    <row r="26" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A26" s="100" t="s">
+        <v>437</v>
+      </c>
+      <c r="B26" s="100">
+        <v>1</v>
+      </c>
+      <c r="C26" s="100"/>
+      <c r="D26" s="124" t="s">
+        <v>448</v>
+      </c>
+      <c r="E26" s="124"/>
+      <c r="F26" s="124"/>
+      <c r="G26" s="124"/>
+      <c r="H26" s="124"/>
+      <c r="I26" s="124"/>
+      <c r="J26" s="124"/>
+      <c r="K26" s="100"/>
+      <c r="L26" s="100"/>
+      <c r="M26" s="100"/>
+      <c r="N26" s="100"/>
+    </row>
+    <row r="27" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A27" s="100" t="s">
+        <v>449</v>
+      </c>
+      <c r="B27" s="100">
+        <v>2</v>
+      </c>
+      <c r="C27" s="100"/>
+      <c r="D27" s="124" t="s">
+        <v>450</v>
+      </c>
+      <c r="E27" s="124"/>
+      <c r="F27" s="124"/>
+      <c r="G27" s="124"/>
+      <c r="H27" s="124"/>
+      <c r="I27" s="124"/>
+      <c r="J27" s="124"/>
+      <c r="K27" s="124"/>
+      <c r="L27" s="100"/>
+      <c r="M27" s="100"/>
+      <c r="N27" s="100"/>
+    </row>
+    <row r="28" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A28" s="100" t="s">
+        <v>451</v>
+      </c>
+      <c r="B28" s="100">
+        <v>1</v>
+      </c>
+      <c r="C28" s="100"/>
+      <c r="D28" s="124" t="s">
+        <v>452</v>
+      </c>
+      <c r="E28" s="124"/>
+      <c r="F28" s="124"/>
+      <c r="G28" s="124"/>
+      <c r="H28" s="124"/>
+      <c r="I28" s="124"/>
+      <c r="J28" s="124"/>
+      <c r="K28" s="100"/>
+      <c r="L28" s="100"/>
+      <c r="M28" s="100"/>
+      <c r="N28" s="100"/>
+    </row>
+    <row r="29" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A29" s="102" t="s">
+        <v>453</v>
+      </c>
+      <c r="B29" s="122">
+        <v>8100</v>
+      </c>
+      <c r="C29" s="100"/>
+      <c r="D29" s="124" t="s">
+        <v>454</v>
+      </c>
+      <c r="E29" s="124"/>
+      <c r="F29" s="124"/>
+      <c r="G29" s="124"/>
+      <c r="H29" s="124"/>
+      <c r="I29" s="124"/>
+      <c r="J29" s="124"/>
+      <c r="K29" s="100"/>
+      <c r="L29" s="100"/>
+      <c r="M29" s="100"/>
+      <c r="N29" s="100"/>
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A30" s="100" t="s">
+        <v>455</v>
+      </c>
+      <c r="B30" s="116">
+        <v>-500</v>
+      </c>
+      <c r="C30" s="100"/>
+      <c r="D30" s="123"/>
+      <c r="E30" s="100"/>
+      <c r="F30" s="100"/>
+      <c r="G30" s="100"/>
+      <c r="H30" s="100"/>
+      <c r="I30" s="100"/>
+      <c r="J30" s="100"/>
+      <c r="K30" s="100"/>
+      <c r="L30" s="100"/>
+      <c r="M30" s="100"/>
+      <c r="N30" s="100"/>
+    </row>
+    <row r="31" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A31" s="100" t="s">
+        <v>456</v>
+      </c>
+      <c r="B31" s="116">
+        <v>750</v>
+      </c>
+      <c r="C31" s="100"/>
+      <c r="D31" s="120" t="s">
+        <v>457</v>
+      </c>
+      <c r="E31" s="100"/>
+      <c r="F31" s="100"/>
+      <c r="G31" s="100"/>
+      <c r="H31" s="100"/>
+      <c r="I31" s="100"/>
+      <c r="J31" s="100"/>
+      <c r="K31" s="100"/>
+      <c r="L31" s="100"/>
+      <c r="M31" s="100"/>
+      <c r="N31" s="100"/>
+    </row>
+    <row r="32" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A32" s="100" t="s">
+        <v>458</v>
+      </c>
+      <c r="B32" s="116">
+        <v>9800</v>
+      </c>
+      <c r="C32" s="100"/>
+      <c r="D32" s="125" t="s">
+        <v>459</v>
+      </c>
+      <c r="E32" s="125"/>
+      <c r="F32" s="125"/>
+      <c r="G32" s="125"/>
+      <c r="H32" s="125"/>
+      <c r="I32" s="125"/>
+      <c r="J32" s="100"/>
+      <c r="K32" s="100"/>
+      <c r="L32" s="100"/>
+      <c r="M32" s="100"/>
+      <c r="N32" s="100"/>
+    </row>
+    <row r="33" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A33" s="100" t="s">
+        <v>460</v>
+      </c>
+      <c r="B33" s="116">
+        <v>-1950</v>
+      </c>
+      <c r="C33" s="100"/>
+      <c r="D33" s="100"/>
+      <c r="E33" s="100"/>
+      <c r="F33" s="100"/>
+      <c r="G33" s="100"/>
+      <c r="H33" s="100"/>
+      <c r="I33" s="100"/>
+      <c r="J33" s="100"/>
+      <c r="K33" s="100"/>
+      <c r="L33" s="100"/>
+      <c r="M33" s="100"/>
+      <c r="N33" s="100"/>
+    </row>
+    <row r="34" spans="1:14" x14ac:dyDescent="0.2">
+      <c r="A34" s="102" t="s">
+        <v>461</v>
+      </c>
+      <c r="B34" s="102" t="s">
+        <v>462</v>
+      </c>
+      <c r="C34" s="102"/>
+      <c r="D34" s="100"/>
+      <c r="E34" s="100"/>
+      <c r="F34" s="100"/>
+      <c r="G34" s="100"/>
+      <c r="H34" s="100"/>
+      <c r="I34" s="100"/>
+      <c r="J34" s="100"/>
+      <c r="K34" s="100"/>
+      <c r="L34" s="100"/>
+      <c r="M34" s="100"/>
+      <c r="N34" s="100"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>